--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260707.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260707.xlsx
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>3,418,000</t>
+          <t>1,333,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,333,000</t>
+          <t>3,418,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>805,897</t>
+          <t>5,699,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,826,000</t>
+          <t>575,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>575,000</t>
+          <t>805,897</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>5,699,000</t>
+          <t>1,826,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>374,000</t>
+          <t>1,192,441</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,192,441</t>
+          <t>374,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>4,436,578</t>
+          <t>1,373,384</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>2,587,703</t>
+          <t>145,386</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>1,373,384</t>
+          <t>2,587,703</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>145,386</t>
+          <t>4,436,578</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>202607WVHFN6F</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>773,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>202607WVHFN6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>773,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>388,000</t>
+          <t>289,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>289,000</t>
+          <t>93,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>93,000</t>
+          <t>388,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>318,000</t>
+          <t>177,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>156,000</t>
+          <t>170,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>1,751,000</t>
+          <t>65,538</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>170,000</t>
+          <t>318,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>65,538</t>
+          <t>156,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>177,000</t>
+          <t>1,751,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>253,000</t>
+          <t>677,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>677,000</t>
+          <t>253,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>334,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>334,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
